--- a/backend/templates/DISBURSEMENT VOUCHER.xlsx
+++ b/backend/templates/DISBURSEMENT VOUCHER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jajrc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\procurement\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B75421-0889-4FE2-A17F-F31E54E67F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDFE0E1-AE85-422F-9FF3-0921BD95D9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DV-PR" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -131,13 +131,113 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">    MARC JUSTIN E. ARZADON</t>
+  </si>
+  <si>
+    <t>(Signature over Printed Name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Manager </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date: </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Century Gothic"/>
       </rPr>
+      <t>C.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>Received Payment:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Check No.: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Name: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR No.: </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>D.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve">Accounting Entries </t>
+    </r>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Account Code</t>
+  </si>
+  <si>
+    <t>Debit</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order No. </t>
+  </si>
+  <si>
+    <t>LYRA JAVONILLO:</t>
+  </si>
+  <si>
+    <t>(Signature over Printed Name- Payee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXAMPLE: PAYMENT FOR THE PROCUREMENT OF MATERIALS </t>
+  </si>
+  <si>
+    <r>
       <t>B.</t>
     </r>
     <r>
@@ -178,120 +278,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">    MARC JUSTIN E. ARZADON</t>
-  </si>
-  <si>
-    <t>(Signature over Printed Name)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Admin / Accounting </t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Manager </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date: </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>C.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>Received Payment:</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Check No.: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Name: </t>
-  </si>
-  <si>
-    <t>(Signature over Printed Name- Payor )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR No.: </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>D.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">Accounting Entries </t>
-    </r>
-  </si>
-  <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>Account Code</t>
-  </si>
-  <si>
-    <t>Debit</t>
-  </si>
-  <si>
-    <t>Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAYMENT FOR THE PROCUREMENT OF MATERIALS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELAINE MARICRIS AGUILAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order No. </t>
+    <t>RONALYN MALLARE</t>
+  </si>
+  <si>
+    <t>ELAINE AGUILAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,13 +396,6 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-    </font>
-    <font>
-      <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -428,6 +418,45 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -437,7 +466,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -496,17 +525,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -517,17 +535,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -600,15 +607,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -841,58 +839,344 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,171 +1185,120 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1088,11 +1321,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>274545</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1095375" cy="342900"/>
+    <xdr:ext cx="1095375" cy="649941"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="image1.png">
@@ -1111,74 +1344,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1095375" cy="342900"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image1.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1095375" cy="342900"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image1.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="274545" y="67235"/>
+          <a:ext cx="1095375" cy="649941"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1398,337 +1567,337 @@
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="27.7109375" customWidth="1"/>
     <col min="7" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:6" ht="15" customHeight="1">
+      <c r="A1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5">
-      <c r="A3" s="26" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" ht="44.25" customHeight="1" thickBot="1">
+      <c r="A2" s="110"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:6" ht="15" customHeight="1">
+      <c r="A4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30" t="s">
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="27" t="s">
+      <c r="F4" s="54"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1">
+      <c r="A5" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="27" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="54"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1">
+      <c r="A6" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="83" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="85"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.5">
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="23"/>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="82" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="84"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="37"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="98"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="37"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A10" s="38" t="s">
+      <c r="B9" s="56"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="98"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A10" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="38" t="s">
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="25"/>
+      <c r="F10" s="95"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
       <c r="E11" s="39"/>
       <c r="F11" s="40"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="48"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="50"/>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
       <c r="E12" s="41"/>
       <c r="F12" s="42"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
+    <row r="13" spans="1:6" ht="15" customHeight="1">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="41"/>
       <c r="F13" s="42"/>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="50"/>
+    <row r="14" spans="1:6" ht="15" customHeight="1">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
       <c r="E14" s="41"/>
       <c r="F14" s="42"/>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="48"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="50"/>
+    <row r="15" spans="1:6" ht="15" customHeight="1">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
       <c r="E15" s="41"/>
       <c r="F15" s="42"/>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="48"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+    <row r="16" spans="1:6" ht="15" customHeight="1">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
       <c r="E16" s="41"/>
       <c r="F16" s="42"/>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="48"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+    <row r="17" spans="1:6" ht="15" customHeight="1">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="49"/>
       <c r="E17" s="41"/>
       <c r="F17" s="42"/>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="48"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
+    <row r="18" spans="1:6" ht="15" customHeight="1">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="41"/>
       <c r="F18" s="42"/>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="48"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="50"/>
+    <row r="19" spans="1:6" ht="15" customHeight="1">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
       <c r="E19" s="41"/>
       <c r="F19" s="42"/>
     </row>
     <row r="20" spans="1:6" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A20" s="51"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="53"/>
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
       <c r="E20" s="43"/>
       <c r="F20" s="44"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="62" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="114" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="89"/>
+      <c r="F21" s="90"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="36"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="86"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="116"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="22"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="63"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="65" t="s">
+      <c r="E23" s="83"/>
+      <c r="F23" s="84"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="115" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="116"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="29"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="69" t="s">
+      <c r="E24" s="79"/>
+      <c r="F24" s="80"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="116"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="29"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="60" t="s">
+      <c r="E25" s="77"/>
+      <c r="F25" s="78"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="34"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="73" t="s">
+      <c r="B27" s="26">
+        <v>46065</v>
+      </c>
+      <c r="C27" s="74"/>
+      <c r="D27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="7" t="s">
+      <c r="E27" s="26">
+        <v>46065</v>
+      </c>
+      <c r="F27" s="74"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="61">
-        <v>46065</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="61">
-        <v>46065</v>
-      </c>
-      <c r="F27" s="25"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="22"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="71"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="29"/>
+      <c r="F30" s="67"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="37"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="81"/>
-      <c r="F31" s="37"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="80"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="68"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="31"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
       <c r="D32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="77"/>
-      <c r="F32" s="37"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+        <v>19</v>
+      </c>
+      <c r="E32" s="29"/>
+      <c r="F32" s="67"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="9"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -1736,46 +1905,46 @@
       <c r="E33" s="10"/>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A34" s="54" t="s">
+    <row r="34" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A34" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="93"/>
+    </row>
+    <row r="35" spans="1:6" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A35" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="35" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A35" s="12" t="s">
+      <c r="D35" s="33"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
       <c r="A36" s="14"/>
       <c r="B36" s="15"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="59"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="64"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="72"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
       <c r="F37" s="19"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1"/>
@@ -2743,6 +2912,30 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F20"/>
+    <mergeCell ref="A11:D20"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D25:F25"/>
@@ -2759,30 +2952,6 @@
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F20"/>
-    <mergeCell ref="A11:D20"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
